--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882A7A91-41A0-4E1C-A95D-F070116F7A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAB541B-9867-4AF7-A07F-9DB4ED8144DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>마케팅팀 _ Smart Marketing Hub</t>
   </si>
@@ -301,6 +301,18 @@
   </si>
   <si>
     <t>★★★★</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>영업일보</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>계약전, 시설전, 공급전, 폐전, 용도변경 등</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://daesung-sales-report-app.streamlit.app/%EC%98%81%EC%97%85%ED%98%84%ED%99%A9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -405,7 +417,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -577,6 +589,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -586,7 +622,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -644,6 +680,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -671,13 +716,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1015,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1025,13 +1073,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1074,7 +1122,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="28" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1091,7 +1139,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1106,7 +1154,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1121,7 +1169,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1136,7 +1184,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="26"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="8" t="s">
         <v>22</v>
       </c>
@@ -1151,7 +1199,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="10" t="s">
         <v>26</v>
       </c>
@@ -1199,7 +1247,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="22" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -1216,7 +1264,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="20"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="13" t="s">
         <v>22</v>
       </c>
@@ -1231,7 +1279,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="15" t="s">
         <v>26</v>
       </c>
@@ -1246,7 +1294,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="22" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -1263,7 +1311,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="13" t="s">
         <v>12</v>
       </c>
@@ -1278,7 +1326,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="20"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="13" t="s">
         <v>15</v>
       </c>
@@ -1293,7 +1341,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="20"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="18" t="s">
         <v>61</v>
       </c>
@@ -1303,170 +1351,178 @@
       <c r="D21" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="23"/>
+      <c r="B22" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="24"/>
+      <c r="B23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21"/>
-      <c r="B22" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="15" t="s">
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="23"/>
+      <c r="B25" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="23"/>
+      <c r="B26" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="23"/>
+      <c r="B27" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="23"/>
+      <c r="B28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="24"/>
+      <c r="B29" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="23"/>
+      <c r="B31" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="20"/>
-      <c r="B24" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="20"/>
-      <c r="B25" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="13" t="s">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="24"/>
+      <c r="B32" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="20"/>
-      <c r="B26" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="20"/>
-      <c r="B27" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21"/>
-      <c r="B28" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="20"/>
-      <c r="B30" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="21"/>
-      <c r="B31" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
     </row>
     <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
@@ -1482,14 +1538,21 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A30:A32"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A11"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A24:A29"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1505,17 +1568,18 @@
     <hyperlink ref="D18" r:id="rId10" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
     <hyperlink ref="D19" r:id="rId11" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
     <hyperlink ref="D20" r:id="rId12" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D22" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D23" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D25" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D26" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D27" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D28" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D29" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D30" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D31" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D23" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
+    <hyperlink ref="D24" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D26" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D27" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
+    <hyperlink ref="D28" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
+    <hyperlink ref="D29" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
+    <hyperlink ref="D30" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
+    <hyperlink ref="D31" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D32" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
     <hyperlink ref="D21" r:id="rId22" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D25" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D22" r:id="rId24" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAB541B-9867-4AF7-A07F-9DB4ED8144DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984AAC6E-3898-481C-8937-3FA15B19FF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
   <si>
     <t>마케팅팀 _ Smart Marketing Hub</t>
   </si>
@@ -313,6 +313,27 @@
   </si>
   <si>
     <t>https://daesung-sales-report-app.streamlit.app/%EC%98%81%EC%97%85%ED%98%84%ED%99%A9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>배관투자 승인 내역 관리</t>
+  </si>
+  <si>
+    <t>배관투자 승인 내역 관리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>배관투자 승인 내역 조회</t>
+  </si>
+  <si>
+    <t>배관투자 승인 내역 조회</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pipeline-investment-approval-system-choihanyoub.streamlit.app/</t>
+  </si>
+  <si>
+    <t>https://pipeline-investment-approval-system-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -689,6 +710,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -715,18 +748,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1063,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1073,13 +1094,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1122,7 +1143,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1139,7 +1160,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1154,7 +1175,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1169,7 +1190,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1184,359 +1205,375 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="29"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="8" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="30"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="34"/>
+      <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
     <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="22" t="s">
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E16" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="23"/>
-      <c r="B16" s="13" t="s">
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="27"/>
+      <c r="B17" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="27"/>
+      <c r="B18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E18" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="24"/>
-      <c r="B17" s="15" t="s">
+    <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
+      <c r="B19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B20" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E20" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="23"/>
-      <c r="B19" s="13" t="s">
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27"/>
+      <c r="B21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E21" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="23"/>
-      <c r="B20" s="13" t="s">
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="27"/>
+      <c r="B22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D22" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E22" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="23"/>
-      <c r="B21" s="18" t="s">
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C23" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D23" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E23" s="21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="23"/>
-      <c r="B22" s="32" t="s">
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C24" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D24" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E24" s="25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="24"/>
-      <c r="B23" s="15" t="s">
+    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="28"/>
+      <c r="B25" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="s">
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B26" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C26" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E26" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="23"/>
-      <c r="B25" s="19" t="s">
+    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="27"/>
+      <c r="B27" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C27" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E27" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="23"/>
-      <c r="B26" s="13" t="s">
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="27"/>
+      <c r="B28" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C28" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D28" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="23"/>
-      <c r="B27" s="13" t="s">
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="27"/>
+      <c r="B29" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D29" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E29" s="21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="23"/>
-      <c r="B28" s="13" t="s">
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="27"/>
+      <c r="B30" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D30" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E30" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="24"/>
-      <c r="B29" s="15" t="s">
+    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="28"/>
+      <c r="B31" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C31" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E31" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="s">
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B32" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C32" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D32" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E32" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="23"/>
-      <c r="B31" s="13" t="s">
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="27"/>
+      <c r="B33" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D33" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E33" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="24"/>
-      <c r="B32" s="15" t="s">
+    <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="28"/>
+      <c r="B34" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
@@ -1545,14 +1582,28 @@
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A32:A34"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A26:A31"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -1560,26 +1611,27 @@
     <hyperlink ref="D7" r:id="rId2" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
     <hyperlink ref="D8" r:id="rId3" xr:uid="{A029C8B6-F468-4C9C-BCDF-9334B981A7AA}"/>
     <hyperlink ref="D9" r:id="rId4" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D10" r:id="rId5" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D11" r:id="rId6" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
-    <hyperlink ref="D15" r:id="rId7" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D16" r:id="rId8" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D23" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D24" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D26" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D27" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D28" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D29" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D30" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D31" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D32" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
-    <hyperlink ref="D21" r:id="rId22" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D22" r:id="rId24" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
+    <hyperlink ref="D11" r:id="rId5" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D12" r:id="rId6" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
+    <hyperlink ref="D16" r:id="rId7" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D18" r:id="rId8" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D19" r:id="rId9" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
+    <hyperlink ref="D20" r:id="rId10" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
+    <hyperlink ref="D21" r:id="rId11" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
+    <hyperlink ref="D22" r:id="rId12" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D25" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
+    <hyperlink ref="D26" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D28" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D29" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
+    <hyperlink ref="D30" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
+    <hyperlink ref="D31" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
+    <hyperlink ref="D32" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
+    <hyperlink ref="D33" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D34" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D23" r:id="rId22" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
+    <hyperlink ref="D27" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D24" r:id="rId24" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
+    <hyperlink ref="D17" r:id="rId25" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984AAC6E-3898-481C-8937-3FA15B19FF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6986829-63AF-4D81-B59E-28556604FFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
   <si>
     <t>마케팅팀 _ Smart Marketing Hub</t>
   </si>
@@ -334,6 +334,10 @@
   </si>
   <si>
     <t>https://pipeline-investment-approval-system-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiNTM3OTdlY2UtZWJhMi00ZmY0LWEzZWEtZGJlZTUzZjQ0NDVhIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1183,7 +1187,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>18</v>
@@ -1609,29 +1613,29 @@
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{F1E97151-816F-47B2-B425-70BA6507D2DC}"/>
     <hyperlink ref="D7" r:id="rId2" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{A029C8B6-F468-4C9C-BCDF-9334B981A7AA}"/>
-    <hyperlink ref="D9" r:id="rId4" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D11" r:id="rId5" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D12" r:id="rId6" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
-    <hyperlink ref="D16" r:id="rId7" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D18" r:id="rId8" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D19" r:id="rId9" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
-    <hyperlink ref="D20" r:id="rId10" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
-    <hyperlink ref="D21" r:id="rId11" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
-    <hyperlink ref="D22" r:id="rId12" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D25" r:id="rId13" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D26" r:id="rId14" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D28" r:id="rId15" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D29" r:id="rId16" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D30" r:id="rId17" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D31" r:id="rId18" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D32" r:id="rId19" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D33" r:id="rId20" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D34" r:id="rId21" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D27" r:id="rId23" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D24" r:id="rId24" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
-    <hyperlink ref="D17" r:id="rId25" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D11" r:id="rId4" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D12" r:id="rId5" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D18" r:id="rId7" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D19" r:id="rId8" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
+    <hyperlink ref="D20" r:id="rId9" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
+    <hyperlink ref="D22" r:id="rId11" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
+    <hyperlink ref="D26" r:id="rId13" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D28" r:id="rId14" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D29" r:id="rId15" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
+    <hyperlink ref="D30" r:id="rId16" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
+    <hyperlink ref="D31" r:id="rId17" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
+    <hyperlink ref="D32" r:id="rId18" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
+    <hyperlink ref="D33" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D34" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
+    <hyperlink ref="D27" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D24" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
+    <hyperlink ref="D17" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D8" r:id="rId25" xr:uid="{D3B35CF9-7F2C-4D3D-87A0-F7FA36E4A236}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6986829-63AF-4D81-B59E-28556604FFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DCE562-8AE5-4F26-955E-9B0938CB4595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>마케팅팀 _ Smart Marketing Hub</t>
   </si>
@@ -338,6 +338,159 @@
   </si>
   <si>
     <t>https://app.powerbi.com/view?r=eyJrIjoiNTM3OTdlY2UtZWJhMi00ZmY0LWEzZWEtZGJlZTUzZjQ0NDVhIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://simulation-pipeline-investment-dashboard-3-choihanyoub.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신규배관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Simulation</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경제성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Enhanced version) _ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계량기등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추정기능</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -345,7 +498,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +568,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -647,7 +807,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -724,6 +884,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1088,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1098,13 +1261,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1147,7 +1310,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="33" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1164,7 +1327,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1179,7 +1342,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1194,7 +1357,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1209,7 +1372,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="33"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="8" t="s">
         <v>73</v>
       </c>
@@ -1224,110 +1387,110 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33"/>
-      <c r="B11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>23</v>
+      <c r="A11" s="34"/>
+      <c r="B11" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>82</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="34"/>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="35"/>
+      <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
     <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B16" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E17" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
-      <c r="B17" s="19" t="s">
+    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="28"/>
+      <c r="B18" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C18" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="27"/>
-      <c r="B18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>24</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>25</v>
@@ -1335,256 +1498,264 @@
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="28"/>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="29"/>
+      <c r="B20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D20" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B21" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="13" t="s">
+    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="28"/>
+      <c r="B22" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D22" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E22" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
-      <c r="B22" s="13" t="s">
+    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="28"/>
+      <c r="B23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C23" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D23" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E23" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="27"/>
-      <c r="B23" s="18" t="s">
+    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28"/>
+      <c r="B24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C24" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D24" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="27"/>
-      <c r="B24" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="28"/>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="29"/>
+      <c r="B26" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C26" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D26" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E26" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
+    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B27" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C27" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D27" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E27" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
-      <c r="B27" s="19" t="s">
+    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
+      <c r="B28" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C28" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D28" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="27"/>
-      <c r="B28" s="13" t="s">
+    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="28"/>
+      <c r="B29" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C29" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D29" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E29" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="27"/>
-      <c r="B29" s="13" t="s">
+    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+      <c r="B30" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D30" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E30" s="21" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="27"/>
-      <c r="B30" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="28"/>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="29"/>
+      <c r="B32" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C32" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E32" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="26" t="s">
+    <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B33" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D33" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E33" s="13" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27"/>
-      <c r="B33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="28"/>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="29"/>
+      <c r="B35" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C35" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E35" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
     </row>
     <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
@@ -1600,42 +1771,50 @@
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A33:A35"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A27:A32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{F1E97151-816F-47B2-B425-70BA6507D2DC}"/>
     <hyperlink ref="D7" r:id="rId2" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
     <hyperlink ref="D9" r:id="rId3" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D11" r:id="rId4" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D12" r:id="rId5" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
-    <hyperlink ref="D16" r:id="rId6" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D18" r:id="rId7" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D19" r:id="rId8" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
-    <hyperlink ref="D20" r:id="rId9" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
-    <hyperlink ref="D21" r:id="rId10" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
-    <hyperlink ref="D22" r:id="rId11" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D25" r:id="rId12" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D26" r:id="rId13" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D28" r:id="rId14" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D29" r:id="rId15" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D30" r:id="rId16" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D31" r:id="rId17" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D32" r:id="rId18" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D33" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D34" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
-    <hyperlink ref="D23" r:id="rId21" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D27" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
-    <hyperlink ref="D17" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D12" r:id="rId4" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D13" r:id="rId5" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
+    <hyperlink ref="D17" r:id="rId6" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D19" r:id="rId7" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
+    <hyperlink ref="D21" r:id="rId9" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
+    <hyperlink ref="D22" r:id="rId10" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
+    <hyperlink ref="D23" r:id="rId11" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D26" r:id="rId12" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
+    <hyperlink ref="D27" r:id="rId13" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D29" r:id="rId14" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D30" r:id="rId15" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
+    <hyperlink ref="D31" r:id="rId16" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
+    <hyperlink ref="D32" r:id="rId17" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
+    <hyperlink ref="D33" r:id="rId18" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
+    <hyperlink ref="D34" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D35" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D24" r:id="rId21" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
+    <hyperlink ref="D28" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
+    <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D8" r:id="rId25" xr:uid="{D3B35CF9-7F2C-4D3D-87A0-F7FA36E4A236}"/>
+    <hyperlink ref="D11" r:id="rId26" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DCE562-8AE5-4F26-955E-9B0938CB4595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD0807E-D273-44D8-B3FB-53A63C4F7F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -337,10 +337,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiNTM3OTdlY2UtZWJhMi00ZmY0LWEzZWEtZGJlZTUzZjQ0NDVhIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>https://simulation-pipeline-investment-dashboard-3-choihanyoub.streamlit.app/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -491,6 +487,10 @@
       </rPr>
       <t>추정기능</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +602,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -798,6 +798,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -807,7 +818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,6 +926,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1251,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1260,7 +1274,7 @@
     <col min="5" max="5" width="43.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -1269,21 +1283,21 @@
       <c r="D1" s="31"/>
       <c r="E1" s="32"/>
     </row>
-    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1292,7 +1306,7 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -1309,7 +1323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>7</v>
       </c>
@@ -1326,7 +1340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="34"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
@@ -1341,7 +1355,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="34"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
@@ -1350,13 +1364,14 @@
         <v>16</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="36"/>
+    </row>
+    <row r="9" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="34"/>
       <c r="B9" s="8" t="s">
         <v>19</v>
@@ -1371,7 +1386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="34"/>
       <c r="B10" s="8" t="s">
         <v>73</v>
@@ -1386,22 +1401,22 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="34"/>
       <c r="B11" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>82</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="34"/>
       <c r="B12" s="8" t="s">
         <v>22</v>
@@ -1416,7 +1431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="35"/>
       <c r="B13" s="10" t="s">
         <v>26</v>
@@ -1431,14 +1446,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
@@ -1447,7 +1462,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -1813,8 +1828,8 @@
     <hyperlink ref="D28" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
     <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D8" r:id="rId25" xr:uid="{D3B35CF9-7F2C-4D3D-87A0-F7FA36E4A236}"/>
-    <hyperlink ref="D11" r:id="rId26" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
+    <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{232D672B-7911-4C38-B4B8-69D4CCD14A2A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD0807E-D273-44D8-B3FB-53A63C4F7F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6AA0C7-30D0-466E-A093-0D1604ADDF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -900,6 +900,9 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -926,9 +929,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1275,13 +1275,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1324,7 +1324,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="34" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1341,7 +1341,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="34"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1356,7 +1356,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -1369,10 +1369,10 @@
       <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="36"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="34"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="34"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
         <v>73</v>
       </c>
@@ -1402,7 +1402,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="34"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="26" t="s">
         <v>80</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="34"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="8" t="s">
         <v>22</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="28" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -1497,7 +1497,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="28"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="19" t="s">
         <v>74</v>
       </c>
@@ -1512,7 +1512,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="13" t="s">
         <v>22</v>
       </c>
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="29"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="15" t="s">
         <v>26</v>
       </c>
@@ -1542,7 +1542,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="12" t="s">
@@ -1559,7 +1559,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="28"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="13" t="s">
         <v>12</v>
       </c>
@@ -1574,7 +1574,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="28"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="13" t="s">
         <v>15</v>
       </c>
@@ -1589,7 +1589,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="28"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="18" t="s">
         <v>61</v>
       </c>
@@ -1604,7 +1604,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="28"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="23" t="s">
         <v>70</v>
       </c>
@@ -1619,7 +1619,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="29"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="15" t="s">
         <v>53</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="28" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="28"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="19" t="s">
         <v>64</v>
       </c>
@@ -1666,7 +1666,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="28"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="13" t="s">
         <v>51</v>
       </c>
@@ -1681,7 +1681,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="28"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="13" t="s">
         <v>39</v>
       </c>
@@ -1696,7 +1696,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="28"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="13" t="s">
         <v>42</v>
       </c>
@@ -1711,7 +1711,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="29"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="15" t="s">
         <v>45</v>
       </c>
@@ -1726,7 +1726,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="28" t="s">
         <v>60</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -1743,7 +1743,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="28"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="13" t="s">
         <v>32</v>
       </c>
@@ -1758,7 +1758,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="29"/>
+      <c r="A35" s="30"/>
       <c r="B35" s="15" t="s">
         <v>35</v>
       </c>
@@ -1829,7 +1829,7 @@
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
     <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{232D672B-7911-4C38-B4B8-69D4CCD14A2A}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{74553892-7F82-4888-A609-F49D18D0BD75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6AA0C7-30D0-466E-A093-0D1604ADDF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE43D05-1A52-48D6-B243-B7F3AEE64642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -1829,7 +1829,7 @@
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
     <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{74553892-7F82-4888-A609-F49D18D0BD75}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{50CBD3F9-27B3-4E8A-B479-CC5A6A43900D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE43D05-1A52-48D6-B243-B7F3AEE64642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AA91A3-AAB6-46D0-9F15-E69A6550F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -490,7 +490,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+    <t>https://app.powerbi.com/reportEmbed?reportId=ffbf9cef-c59a-41a6-8cd3-765a31633a25&amp;autoAuth=true&amp;ctid=966ea1f4-b921-40f1-8321-cb1ef2a79660</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AA91A3-AAB6-46D0-9F15-E69A6550F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0BE125-E4D8-4444-BBDA-B64448A2BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -490,7 +490,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/reportEmbed?reportId=ffbf9cef-c59a-41a6-8cd3-765a31633a25&amp;autoAuth=true&amp;ctid=966ea1f4-b921-40f1-8321-cb1ef2a79660</t>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1829,7 +1829,7 @@
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
     <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{50CBD3F9-27B3-4E8A-B479-CC5A6A43900D}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{391E57D7-42E4-4975-8D57-F7094AAFBCF7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0BE125-E4D8-4444-BBDA-B64448A2BC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4706E423-723B-40D7-85DB-22CD653E8655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
@@ -490,7 +490,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiOWIwMDZkYTEtZjM1ZS00NGE3LTg4ODktYTQ2ZjI2OWY5ZDdmIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
+    <t>https://app.powerbi.com/view?r=eyJrIjoiNjA5YzU5YjgtODBkYS00MjQ2LWJmOTItMmRhZWJmYzYxYzMyIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1829,7 +1829,7 @@
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
     <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
     <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{391E57D7-42E4-4975-8D57-F7094AAFBCF7}"/>
+    <hyperlink ref="D8" r:id="rId26" xr:uid="{6BE0E153-80A8-4EA5-BB94-E560DF08CC4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4706E423-723B-40D7-85DB-22CD653E8655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97C0661-6BF2-4854-8465-4F875828610C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
   <si>
     <t>마케팅팀 _ Smart Marketing Hub</t>
   </si>
@@ -492,6 +492,15 @@
   <si>
     <t>https://app.powerbi.com/view?r=eyJrIjoiNjA5YzU5YjgtODBkYS00MjQ2LWJmOTItMmRhZWJmYzYxYzMyIiwidCI6Ijk2NmVhMWY0LWI5MjEtNDBmMS04MzIxLWNiMWVmMmE3OTY2MCJ9</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대용량 수요처 이상 감지 대시보드</t>
+  </si>
+  <si>
+    <t>YoY, 전년대비 10%이상 하락 업체 감지</t>
+  </si>
+  <si>
+    <t>https://large-volume-consumer-anomaly-alert-choihanyoub.streamlit.app/</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE734F67-6E3F-4A0D-AE2A-D52F1874955A}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1745,39 +1754,47 @@
     <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29"/>
       <c r="B34" s="13" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="30"/>
-      <c r="B35" s="15" t="s">
+      <c r="A35" s="29"/>
+      <c r="B35" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="30"/>
+      <c r="B36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C36" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D36" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E36" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
@@ -1793,9 +1810,16 @@
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A33:A36"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A17:A20"/>
@@ -1822,8 +1846,8 @@
     <hyperlink ref="D31" r:id="rId16" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
     <hyperlink ref="D32" r:id="rId17" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
     <hyperlink ref="D33" r:id="rId18" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D34" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D35" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D35" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D36" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
     <hyperlink ref="D24" r:id="rId21" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
     <hyperlink ref="D28" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
     <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>

--- a/marketing_hub.xlsx
+++ b/marketing_hub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\마케팅hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97C0661-6BF2-4854-8465-4F875828610C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83F6BFD-C715-44AC-8D65-CA59B1CE08F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095BD162-3FCA-4CFF-A0FF-4016CECDBBBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>공동주택, 지역난방 시각화, 판매량 비교 등</t>
   </si>
   <si>
-    <t>https://daesung-marketing-dashboard.streamlit.app/</t>
-  </si>
-  <si>
     <t>★★★★★</t>
   </si>
   <si>
@@ -501,6 +498,10 @@
   </si>
   <si>
     <t>https://large-volume-consumer-anomaly-alert-choihanyoub.streamlit.app/</t>
+  </si>
+  <si>
+    <t>https://final-apt-map.streamlit.app/</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1343,116 +1344,116 @@
         <v>9</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="35"/>
       <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35"/>
       <c r="B8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="35"/>
       <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>21</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="35"/>
       <c r="B11" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>81</v>
-      </c>
       <c r="D11" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35"/>
       <c r="B12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="36"/>
       <c r="B13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1464,7 +1465,7 @@
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1490,69 +1491,69 @@
     </row>
     <row r="17" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>21</v>
-      </c>
       <c r="E17" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="29"/>
       <c r="B18" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29"/>
       <c r="B19" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="30"/>
       <c r="B20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>28</v>
-      </c>
       <c r="E20" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>8</v>
@@ -1561,239 +1562,239 @@
         <v>9</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="29"/>
       <c r="B22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>14</v>
-      </c>
       <c r="E22" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="29"/>
       <c r="B23" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>17</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="29"/>
       <c r="B24" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>63</v>
-      </c>
       <c r="E24" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="29"/>
       <c r="B25" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="D25" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="22" t="s">
-        <v>72</v>
-      </c>
       <c r="E25" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="30"/>
       <c r="B26" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="D26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>55</v>
-      </c>
       <c r="E26" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="14" t="s">
-        <v>50</v>
-      </c>
       <c r="E27" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="29"/>
       <c r="B28" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>65</v>
-      </c>
       <c r="D28" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="29"/>
       <c r="B29" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>52</v>
-      </c>
       <c r="E29" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29"/>
       <c r="B30" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>41</v>
-      </c>
       <c r="E30" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="29"/>
       <c r="B31" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="E31" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="30"/>
       <c r="B32" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D32" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>47</v>
-      </c>
       <c r="E32" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="E33" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29"/>
       <c r="B34" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="14" t="s">
-        <v>85</v>
-      </c>
       <c r="E34" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29"/>
       <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="14" t="s">
-        <v>34</v>
-      </c>
       <c r="E35" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="30"/>
       <c r="B36" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="D36" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="E36" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1828,32 +1829,32 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" xr:uid="{F1E97151-816F-47B2-B425-70BA6507D2DC}"/>
-    <hyperlink ref="D7" r:id="rId2" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
-    <hyperlink ref="D9" r:id="rId3" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
-    <hyperlink ref="D13" r:id="rId5" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
-    <hyperlink ref="D17" r:id="rId6" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
-    <hyperlink ref="D19" r:id="rId7" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
-    <hyperlink ref="D20" r:id="rId8" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
-    <hyperlink ref="D21" r:id="rId9" xr:uid="{C1FBCA7A-6843-4B17-AF91-EE372BADDDE6}"/>
-    <hyperlink ref="D22" r:id="rId10" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
-    <hyperlink ref="D23" r:id="rId11" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
-    <hyperlink ref="D26" r:id="rId12" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
-    <hyperlink ref="D27" r:id="rId13" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
-    <hyperlink ref="D29" r:id="rId14" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
-    <hyperlink ref="D30" r:id="rId15" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
-    <hyperlink ref="D31" r:id="rId16" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
-    <hyperlink ref="D32" r:id="rId17" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
-    <hyperlink ref="D33" r:id="rId18" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
-    <hyperlink ref="D35" r:id="rId19" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
-    <hyperlink ref="D36" r:id="rId20" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
-    <hyperlink ref="D24" r:id="rId21" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
-    <hyperlink ref="D28" r:id="rId22" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
-    <hyperlink ref="D18" r:id="rId24" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
-    <hyperlink ref="D11" r:id="rId25" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
-    <hyperlink ref="D8" r:id="rId26" xr:uid="{6BE0E153-80A8-4EA5-BB94-E560DF08CC4C}"/>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{5C1DEC94-2F4B-4133-86D3-AADE1EC5BB7B}"/>
+    <hyperlink ref="D9" r:id="rId2" xr:uid="{69E5F510-DCEE-4DBC-B61D-D16CB34C87B6}"/>
+    <hyperlink ref="D12" r:id="rId3" xr:uid="{629C0BC2-AFDE-4B3F-8122-C8D3BD9C2B3D}"/>
+    <hyperlink ref="D13" r:id="rId4" xr:uid="{18DA179E-DE32-4D35-B9E1-21A5601866FD}"/>
+    <hyperlink ref="D17" r:id="rId5" xr:uid="{46B60EA8-B2A3-4B72-B267-01E93544A41A}"/>
+    <hyperlink ref="D19" r:id="rId6" xr:uid="{879D1E95-6BC7-48BC-B1C3-A209811C7D3A}"/>
+    <hyperlink ref="D20" r:id="rId7" xr:uid="{7556C996-B8A7-434D-9D62-16C7A446460A}"/>
+    <hyperlink ref="D22" r:id="rId8" xr:uid="{34ED876C-4C80-40B4-9214-C90A9ACD0562}"/>
+    <hyperlink ref="D23" r:id="rId9" xr:uid="{97C5255C-1EE7-4EBD-93D8-C990E49FDE5E}"/>
+    <hyperlink ref="D26" r:id="rId10" xr:uid="{BAAC96C8-A8C7-420C-AEB9-B7DBE3AC0272}"/>
+    <hyperlink ref="D27" r:id="rId11" xr:uid="{F4F3E5B9-8A84-4162-B3F7-6049140091E1}"/>
+    <hyperlink ref="D29" r:id="rId12" xr:uid="{133C2513-6F68-4BB8-A22C-F4E12E05D8EE}"/>
+    <hyperlink ref="D30" r:id="rId13" xr:uid="{9D5EEE19-CBE2-4A92-81E4-5CCEFA4A782B}"/>
+    <hyperlink ref="D31" r:id="rId14" xr:uid="{901B1F29-6F8B-44A8-B73D-ECB33B4EC173}"/>
+    <hyperlink ref="D32" r:id="rId15" xr:uid="{FA2B4AB3-D3AD-4C45-B9AE-CB9894236C68}"/>
+    <hyperlink ref="D33" r:id="rId16" xr:uid="{46BC9914-DB59-44C2-AE1D-7DBE840FDF87}"/>
+    <hyperlink ref="D35" r:id="rId17" xr:uid="{C7D853A5-8AC2-48EE-9D09-F56A817230B3}"/>
+    <hyperlink ref="D36" r:id="rId18" xr:uid="{777FEE0E-6AA0-4D34-A657-F4F721388827}"/>
+    <hyperlink ref="D24" r:id="rId19" xr:uid="{A009F8D5-5006-411F-8ACC-D061DC6602FA}"/>
+    <hyperlink ref="D28" r:id="rId20" xr:uid="{8F098067-92A2-4D1B-92BB-D7B15D11F4BD}"/>
+    <hyperlink ref="D25" r:id="rId21" xr:uid="{1AC7A69F-23B4-4813-A045-1E59F9E97CD7}"/>
+    <hyperlink ref="D18" r:id="rId22" xr:uid="{989C5184-1BFA-4F81-95C0-FD43CDF1CE5A}"/>
+    <hyperlink ref="D11" r:id="rId23" xr:uid="{33BD9926-17A9-47CC-A7C5-3C9BA71DD06D}"/>
+    <hyperlink ref="D8" r:id="rId24" xr:uid="{6BE0E153-80A8-4EA5-BB94-E560DF08CC4C}"/>
+    <hyperlink ref="D6" r:id="rId25" xr:uid="{4591B07B-F542-4FDB-96D3-B7D18C020FB2}"/>
+    <hyperlink ref="D21" r:id="rId26" xr:uid="{877E0C23-0647-4B79-AC70-2F24AFF0B031}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
